--- a/backend/wp_templates/L/L8 财务费用.xlsx
+++ b/backend/wp_templates/L/L8 财务费用.xlsx
@@ -10442,7 +10442,7 @@
       <c r="L9" s="146"/>
       <c r="M9" s="146"/>
       <c r="N9" s="147">
-        <f t="shared" ref="N9:N21" si="0">SUM(B9:M9)</f>
+        <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
       <c r="O9" s="146"/>
@@ -10460,7 +10460,7 @@
       <c r="U9" s="149"/>
       <c r="V9" s="149"/>
       <c r="W9" s="147">
-        <f t="shared" ref="W9:W22" si="1">T9+U9+V9</f>
+        <f>T9+U9+V9</f>
         <v>0</v>
       </c>
     </row>
@@ -10481,13 +10481,13 @@
       <c r="L10" s="146"/>
       <c r="M10" s="146"/>
       <c r="N10" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B10:M10)</f>
         <v>0</v>
       </c>
       <c r="O10" s="149"/>
       <c r="P10" s="149"/>
       <c r="Q10" s="147">
-        <f t="shared" ref="Q10:Q21" si="2">N10+O10+P10</f>
+        <f>N10+O10+P10</f>
         <v>0</v>
       </c>
       <c r="R10" s="151">
@@ -10499,7 +10499,7 @@
       <c r="U10" s="149"/>
       <c r="V10" s="149"/>
       <c r="W10" s="147">
-        <f t="shared" si="1"/>
+        <f>T10+U10+V10</f>
         <v>0</v>
       </c>
     </row>
@@ -10512,43 +10512,43 @@
         <v>0</v>
       </c>
       <c r="C11" s="147">
-        <f t="shared" ref="C11:L11" si="3">C9-C10</f>
+        <f>C9-C10</f>
         <v>0</v>
       </c>
       <c r="D11" s="147">
-        <f t="shared" si="3"/>
+        <f>D9-D10</f>
         <v>0</v>
       </c>
       <c r="E11" s="147">
-        <f t="shared" si="3"/>
+        <f>E9-E10</f>
         <v>0</v>
       </c>
       <c r="F11" s="147">
-        <f t="shared" si="3"/>
+        <f>F9-F10</f>
         <v>0</v>
       </c>
       <c r="G11" s="147">
-        <f t="shared" si="3"/>
+        <f>G9-G10</f>
         <v>0</v>
       </c>
       <c r="H11" s="147">
-        <f t="shared" si="3"/>
+        <f>H9-H10</f>
         <v>0</v>
       </c>
       <c r="I11" s="147">
-        <f t="shared" si="3"/>
+        <f>I9-I10</f>
         <v>0</v>
       </c>
       <c r="J11" s="147">
-        <f t="shared" si="3"/>
+        <f>J9-J10</f>
         <v>0</v>
       </c>
       <c r="K11" s="147">
-        <f t="shared" si="3"/>
+        <f>K9-K10</f>
         <v>0</v>
       </c>
       <c r="L11" s="147">
-        <f t="shared" si="3"/>
+        <f>L9-L10</f>
         <v>0</v>
       </c>
       <c r="M11" s="147">
@@ -10560,11 +10560,11 @@
         <v>0</v>
       </c>
       <c r="O11" s="147">
-        <f t="shared" ref="O11:P11" si="4">O9-O10</f>
+        <f>O9-O10</f>
         <v>0</v>
       </c>
       <c r="P11" s="147">
-        <f t="shared" si="4"/>
+        <f>P9-P10</f>
         <v>0</v>
       </c>
       <c r="Q11" s="147">
@@ -10580,7 +10580,7 @@
       <c r="U11" s="147"/>
       <c r="V11" s="147"/>
       <c r="W11" s="147">
-        <f t="shared" si="1"/>
+        <f>T11+U11+V11</f>
         <v>0</v>
       </c>
     </row>
@@ -10601,13 +10601,13 @@
       <c r="L12" s="146"/>
       <c r="M12" s="146"/>
       <c r="N12" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B12:M12)</f>
         <v>0</v>
       </c>
       <c r="O12" s="149"/>
       <c r="P12" s="149"/>
       <c r="Q12" s="147">
-        <f t="shared" si="2"/>
+        <f>N12+O12+P12</f>
         <v>0</v>
       </c>
       <c r="R12" s="151">
@@ -10619,7 +10619,7 @@
       <c r="U12" s="149"/>
       <c r="V12" s="149"/>
       <c r="W12" s="147">
-        <f t="shared" si="1"/>
+        <f>T12+U12+V12</f>
         <v>0</v>
       </c>
     </row>
@@ -10632,43 +10632,43 @@
         <v>0</v>
       </c>
       <c r="C13" s="147">
-        <f t="shared" ref="C13:L13" si="5">C11-C12</f>
+        <f>C11-C12</f>
         <v>0</v>
       </c>
       <c r="D13" s="147">
-        <f t="shared" si="5"/>
+        <f>D11-D12</f>
         <v>0</v>
       </c>
       <c r="E13" s="147">
-        <f t="shared" si="5"/>
+        <f>E11-E12</f>
         <v>0</v>
       </c>
       <c r="F13" s="147">
-        <f t="shared" si="5"/>
+        <f>F11-F12</f>
         <v>0</v>
       </c>
       <c r="G13" s="147">
-        <f t="shared" si="5"/>
+        <f>G11-G12</f>
         <v>0</v>
       </c>
       <c r="H13" s="147">
-        <f t="shared" si="5"/>
+        <f>H11-H12</f>
         <v>0</v>
       </c>
       <c r="I13" s="147">
-        <f t="shared" si="5"/>
+        <f>I11-I12</f>
         <v>0</v>
       </c>
       <c r="J13" s="147">
-        <f t="shared" si="5"/>
+        <f>J11-J12</f>
         <v>0</v>
       </c>
       <c r="K13" s="147">
-        <f t="shared" si="5"/>
+        <f>K11-K12</f>
         <v>0</v>
       </c>
       <c r="L13" s="147">
-        <f t="shared" si="5"/>
+        <f>L11-L12</f>
         <v>0</v>
       </c>
       <c r="M13" s="147">
@@ -10676,19 +10676,19 @@
         <v>0</v>
       </c>
       <c r="N13" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B13:M13)</f>
         <v>0</v>
       </c>
       <c r="O13" s="147">
-        <f t="shared" ref="O13:P13" si="6">O11-O12</f>
+        <f>O11-O12</f>
         <v>0</v>
       </c>
       <c r="P13" s="147">
-        <f t="shared" si="6"/>
+        <f>P11-P12</f>
         <v>0</v>
       </c>
       <c r="Q13" s="147">
-        <f t="shared" si="2"/>
+        <f>N13+O13+P13</f>
         <v>0</v>
       </c>
       <c r="R13" s="151">
@@ -10700,7 +10700,7 @@
       <c r="U13" s="147"/>
       <c r="V13" s="147"/>
       <c r="W13" s="147">
-        <f t="shared" si="1"/>
+        <f>T13+U13+V13</f>
         <v>0</v>
       </c>
     </row>
@@ -10721,17 +10721,17 @@
       <c r="L14" s="149"/>
       <c r="M14" s="149"/>
       <c r="N14" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B14:M14)</f>
         <v>0</v>
       </c>
       <c r="O14" s="164"/>
       <c r="P14" s="164"/>
       <c r="Q14" s="147">
-        <f t="shared" si="2"/>
+        <f>N14+O14+P14</f>
         <v>0</v>
       </c>
       <c r="R14" s="151">
-        <f t="shared" ref="R14:R15" si="7">IF(Q14=0,0,Q14/$Q$22)</f>
+        <f>IF(Q14=0,0,Q14/$Q$22)</f>
         <v>0</v>
       </c>
       <c r="S14" s="173"/>
@@ -10739,7 +10739,7 @@
       <c r="U14" s="164"/>
       <c r="V14" s="164"/>
       <c r="W14" s="147">
-        <f t="shared" si="1"/>
+        <f>T14+U14+V14</f>
         <v>0</v>
       </c>
     </row>
@@ -10760,17 +10760,17 @@
       <c r="L15" s="149"/>
       <c r="M15" s="149"/>
       <c r="N15" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B15:M15)</f>
         <v>0</v>
       </c>
       <c r="O15" s="164"/>
       <c r="P15" s="164"/>
       <c r="Q15" s="147">
-        <f t="shared" si="2"/>
+        <f>N15+O15+P15</f>
         <v>0</v>
       </c>
       <c r="R15" s="151">
-        <f t="shared" si="7"/>
+        <f>IF(Q15=0,0,Q15/$Q$22)</f>
         <v>0</v>
       </c>
       <c r="S15" s="173"/>
@@ -10778,7 +10778,7 @@
       <c r="U15" s="164"/>
       <c r="V15" s="164"/>
       <c r="W15" s="147">
-        <f t="shared" si="1"/>
+        <f>T15+U15+V15</f>
         <v>0</v>
       </c>
     </row>
@@ -10799,17 +10799,17 @@
       <c r="L16" s="146"/>
       <c r="M16" s="146"/>
       <c r="N16" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B16:M16)</f>
         <v>0</v>
       </c>
       <c r="O16" s="149"/>
       <c r="P16" s="149"/>
       <c r="Q16" s="147">
-        <f t="shared" si="2"/>
+        <f>N16+O16+P16</f>
         <v>0</v>
       </c>
       <c r="R16" s="151">
-        <f t="shared" ref="R16:R22" si="8">IF(Q16=0,0,Q16/$Q$22)</f>
+        <f>IF(Q16=0,0,Q16/$Q$22)</f>
         <v>0</v>
       </c>
       <c r="S16" s="173"/>
@@ -10817,7 +10817,7 @@
       <c r="U16" s="149"/>
       <c r="V16" s="149"/>
       <c r="W16" s="147">
-        <f t="shared" si="1"/>
+        <f>T16+U16+V16</f>
         <v>0</v>
       </c>
     </row>
@@ -10838,17 +10838,17 @@
       <c r="L17" s="146"/>
       <c r="M17" s="146"/>
       <c r="N17" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B17:M17)</f>
         <v>0</v>
       </c>
       <c r="O17" s="146"/>
       <c r="P17" s="146"/>
       <c r="Q17" s="147">
-        <f t="shared" si="2"/>
+        <f>N17+O17+P17</f>
         <v>0</v>
       </c>
       <c r="R17" s="151">
-        <f t="shared" si="8"/>
+        <f>IF(Q17=0,0,Q17/$Q$22)</f>
         <v>0</v>
       </c>
       <c r="S17" s="174"/>
@@ -10856,7 +10856,7 @@
       <c r="U17" s="146"/>
       <c r="V17" s="146"/>
       <c r="W17" s="147">
-        <f t="shared" si="1"/>
+        <f>T17+U17+V17</f>
         <v>0</v>
       </c>
     </row>
@@ -10877,17 +10877,17 @@
       <c r="L18" s="146"/>
       <c r="M18" s="146"/>
       <c r="N18" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B18:M18)</f>
         <v>0</v>
       </c>
       <c r="O18" s="146"/>
       <c r="P18" s="146"/>
       <c r="Q18" s="147">
-        <f t="shared" si="2"/>
+        <f>N18+O18+P18</f>
         <v>0</v>
       </c>
       <c r="R18" s="151">
-        <f t="shared" si="8"/>
+        <f>IF(Q18=0,0,Q18/$Q$22)</f>
         <v>0</v>
       </c>
       <c r="S18" s="174"/>
@@ -10895,7 +10895,7 @@
       <c r="U18" s="146"/>
       <c r="V18" s="146"/>
       <c r="W18" s="147">
-        <f t="shared" si="1"/>
+        <f>T18+U18+V18</f>
         <v>0</v>
       </c>
     </row>
@@ -10916,17 +10916,17 @@
       <c r="L19" s="146"/>
       <c r="M19" s="146"/>
       <c r="N19" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B19:M19)</f>
         <v>0</v>
       </c>
       <c r="O19" s="146"/>
       <c r="P19" s="146"/>
       <c r="Q19" s="147">
-        <f t="shared" si="2"/>
+        <f>N19+O19+P19</f>
         <v>0</v>
       </c>
       <c r="R19" s="151">
-        <f t="shared" si="8"/>
+        <f>IF(Q19=0,0,Q19/$Q$22)</f>
         <v>0</v>
       </c>
       <c r="S19" s="174"/>
@@ -10934,7 +10934,7 @@
       <c r="U19" s="146"/>
       <c r="V19" s="146"/>
       <c r="W19" s="147">
-        <f t="shared" si="1"/>
+        <f>T19+U19+V19</f>
         <v>0</v>
       </c>
     </row>
@@ -10947,43 +10947,43 @@
         <v>0</v>
       </c>
       <c r="C20" s="147">
-        <f t="shared" ref="C20:P20" si="9">C17-C18-C19</f>
+        <f>C17-C18-C19</f>
         <v>0</v>
       </c>
       <c r="D20" s="147">
-        <f t="shared" si="9"/>
+        <f>D17-D18-D19</f>
         <v>0</v>
       </c>
       <c r="E20" s="147">
-        <f t="shared" si="9"/>
+        <f>E17-E18-E19</f>
         <v>0</v>
       </c>
       <c r="F20" s="147">
-        <f t="shared" si="9"/>
+        <f>F17-F18-F19</f>
         <v>0</v>
       </c>
       <c r="G20" s="147">
-        <f t="shared" si="9"/>
+        <f>G17-G18-G19</f>
         <v>0</v>
       </c>
       <c r="H20" s="147">
-        <f t="shared" si="9"/>
+        <f>H17-H18-H19</f>
         <v>0</v>
       </c>
       <c r="I20" s="147">
-        <f t="shared" si="9"/>
+        <f>I17-I18-I19</f>
         <v>0</v>
       </c>
       <c r="J20" s="147">
-        <f t="shared" si="9"/>
+        <f>J17-J18-J19</f>
         <v>0</v>
       </c>
       <c r="K20" s="147">
-        <f t="shared" si="9"/>
+        <f>K17-K18-K19</f>
         <v>0</v>
       </c>
       <c r="L20" s="147">
-        <f t="shared" si="9"/>
+        <f>L17-L18-L19</f>
         <v>0</v>
       </c>
       <c r="M20" s="147">
@@ -10991,7 +10991,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B20:M20)</f>
         <v>0</v>
       </c>
       <c r="O20" s="147">
@@ -10999,15 +10999,15 @@
         <v>0</v>
       </c>
       <c r="P20" s="147">
-        <f t="shared" si="9"/>
+        <f>P17-P18-P19</f>
         <v>0</v>
       </c>
       <c r="Q20" s="147">
-        <f t="shared" si="2"/>
+        <f>N20+O20+P20</f>
         <v>0</v>
       </c>
       <c r="R20" s="151">
-        <f t="shared" si="8"/>
+        <f>IF(Q20=0,0,Q20/$Q$22)</f>
         <v>0</v>
       </c>
       <c r="S20" s="299"/>
@@ -11016,15 +11016,15 @@
         <v>0</v>
       </c>
       <c r="U20" s="147">
-        <f t="shared" ref="U20" si="10">U17-U18-U19</f>
+        <f>U17-U18-U19</f>
         <v>0</v>
       </c>
       <c r="V20" s="147">
-        <f t="shared" ref="V20" si="11">V17-V18-V19</f>
+        <f>V17-V18-V19</f>
         <v>0</v>
       </c>
       <c r="W20" s="147">
-        <f t="shared" si="1"/>
+        <f>T20+U20+V20</f>
         <v>0</v>
       </c>
     </row>
@@ -11045,17 +11045,17 @@
       <c r="L21" s="146"/>
       <c r="M21" s="146"/>
       <c r="N21" s="147">
-        <f t="shared" si="0"/>
+        <f>SUM(B21:M21)</f>
         <v>0</v>
       </c>
       <c r="O21" s="146"/>
       <c r="P21" s="146"/>
       <c r="Q21" s="147">
-        <f t="shared" si="2"/>
+        <f>N21+O21+P21</f>
         <v>0</v>
       </c>
       <c r="R21" s="151">
-        <f t="shared" si="8"/>
+        <f>IF(Q21=0,0,Q21/$Q$22)</f>
         <v>0</v>
       </c>
       <c r="S21" s="174"/>
@@ -11063,7 +11063,7 @@
       <c r="U21" s="146"/>
       <c r="V21" s="146"/>
       <c r="W21" s="147">
-        <f t="shared" si="1"/>
+        <f>T21+U21+V21</f>
         <v>0</v>
       </c>
     </row>
@@ -11076,51 +11076,51 @@
         <v>0</v>
       </c>
       <c r="C22" s="147">
-        <f t="shared" ref="C22:P22" si="12">C13+C14-C15+C16+C20+C21</f>
+        <f>C13+C14-C15+C16+C20+C21</f>
         <v>0</v>
       </c>
       <c r="D22" s="147">
-        <f t="shared" si="12"/>
+        <f>D13+D14-D15+D16+D20+D21</f>
         <v>0</v>
       </c>
       <c r="E22" s="147">
-        <f t="shared" si="12"/>
+        <f>E13+E14-E15+E16+E20+E21</f>
         <v>0</v>
       </c>
       <c r="F22" s="147">
-        <f t="shared" si="12"/>
+        <f>F13+F14-F15+F16+F20+F21</f>
         <v>0</v>
       </c>
       <c r="G22" s="147">
-        <f t="shared" si="12"/>
+        <f>G13+G14-G15+G16+G20+G21</f>
         <v>0</v>
       </c>
       <c r="H22" s="147">
-        <f t="shared" si="12"/>
+        <f>H13+H14-H15+H16+H20+H21</f>
         <v>0</v>
       </c>
       <c r="I22" s="147">
-        <f t="shared" si="12"/>
+        <f>I13+I14-I15+I16+I20+I21</f>
         <v>0</v>
       </c>
       <c r="J22" s="147">
-        <f t="shared" si="12"/>
+        <f>J13+J14-J15+J16+J20+J21</f>
         <v>0</v>
       </c>
       <c r="K22" s="147">
-        <f t="shared" si="12"/>
+        <f>K13+K14-K15+K16+K20+K21</f>
         <v>0</v>
       </c>
       <c r="L22" s="147">
-        <f t="shared" si="12"/>
+        <f>L13+L14-L15+L16+L20+L21</f>
         <v>0</v>
       </c>
       <c r="M22" s="147">
-        <f t="shared" si="12"/>
+        <f>M13+M14-M15+M16+M20+M21</f>
         <v>0</v>
       </c>
       <c r="N22" s="147">
-        <f t="shared" si="12"/>
+        <f>N13+N14-N15+N16+N20+N21</f>
         <v>0</v>
       </c>
       <c r="O22" s="147">
@@ -11128,7 +11128,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="147">
-        <f t="shared" si="12"/>
+        <f>P13+P14-P15+P16+P20+P21</f>
         <v>0</v>
       </c>
       <c r="Q22" s="147">
@@ -11136,24 +11136,24 @@
         <v>0</v>
       </c>
       <c r="R22" s="151">
-        <f t="shared" si="8"/>
+        <f>IF(Q22=0,0,Q22/$Q$22)</f>
         <v>0</v>
       </c>
       <c r="S22" s="299"/>
       <c r="T22" s="147">
-        <f t="shared" ref="T22:V22" si="13">T13+T14-T15+T16+T20+T21</f>
+        <f>T13+T14-T15+T16+T20+T21</f>
         <v>0</v>
       </c>
       <c r="U22" s="147">
-        <f t="shared" si="13"/>
+        <f>U13+U14-U15+U16+U20+U21</f>
         <v>0</v>
       </c>
       <c r="V22" s="147">
-        <f t="shared" si="13"/>
+        <f>V13+V14-V15+V16+V20+V21</f>
         <v>0</v>
       </c>
       <c r="W22" s="147">
-        <f t="shared" si="1"/>
+        <f>T22+U22+V22</f>
         <v>0</v>
       </c>
     </row>
@@ -11166,51 +11166,51 @@
         <v>0</v>
       </c>
       <c r="C23" s="151">
-        <f t="shared" ref="C23:N23" si="14">IF($N$22=0,0,C22/$N$22)</f>
+        <f>IF($N$22=0,0,C22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="D23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,D22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="E23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,E22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="F23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,F22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="G23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,G22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="H23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,H22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="I23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,I22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="J23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,J22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="K23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,K22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="L23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,L22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="M23" s="151">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,M22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="N23" s="165">
-        <f t="shared" si="14"/>
+        <f>IF($N$22=0,0,N22/$N$22)</f>
         <v>0</v>
       </c>
       <c r="O23" s="301"/>
